--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300" tabRatio="723" firstSheet="1" activeTab="7"/>
+    <workbookView windowHeight="15220" tabRatio="723" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,14 @@
     <sheet name="2026-07流水" sheetId="7" r:id="rId7"/>
     <sheet name="2026-08流水" sheetId="8" r:id="rId8"/>
     <sheet name="2026-09流水" sheetId="9" r:id="rId9"/>
+    <sheet name="2026-10流水" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="904" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="217">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -652,6 +653,27 @@
   </si>
   <si>
     <t>老池垫付相关</t>
+  </si>
+  <si>
+    <t>牛筋丸5包</t>
+  </si>
+  <si>
+    <t>京东刷单</t>
+  </si>
+  <si>
+    <t>可乐一箱</t>
+  </si>
+  <si>
+    <t>紫菜一包</t>
+  </si>
+  <si>
+    <t>火鸡面</t>
+  </si>
+  <si>
+    <t>快驴</t>
+  </si>
+  <si>
+    <t>烧麦</t>
   </si>
 </sst>
 </file>
@@ -660,12 +682,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -722,11 +744,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -738,16 +791,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -784,17 +837,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -809,44 +868,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -933,7 +955,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -945,19 +1015,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -969,19 +1063,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -993,115 +1117,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1185,11 +1207,56 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1220,36 +1287,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1258,157 +1295,142 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="31" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1417,114 +1439,114 @@
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1534,13 +1556,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1642,7 +1664,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1845,8 +1867,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="支出明细26049_111914" displayName="支出明细26049_111914" ref="A43:C53">
-  <autoFilter ref="A43:C53"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="支出明细26049_111914" displayName="支出明细26049_111914" ref="A43:C61">
+  <autoFilter ref="A43:C61"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
     <tableColumn id="2" name="分类"/>
@@ -1870,6 +1892,30 @@
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C52">
+  <autoFilter ref="A43:C52"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="支出明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="收入明细260410_1220131517" displayName="收入明细260410_1220131517" ref="A33:C40">
+  <autoFilter ref="A33:C40"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="收入明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="支出明细26049_1119141618" displayName="支出明细26049_1119141618" ref="A43:C52">
   <autoFilter ref="A43:C52"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
@@ -2759,6 +2805,489 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="30.625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8">
+        <f>SUM(收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="11">
+        <f>SUM(支出明细26049_1119141618[支出明细])</f>
+        <v>15833</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="14">
+        <f>$B$3-SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14">
+        <f>$B$3-$B$4</f>
+        <v>-15833</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="16" t="e">
+        <f>$B$5/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="16" t="e">
+        <f>$B$6/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"淘宝外卖",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="16" t="e">
+        <f>$B$13/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"美团外卖",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="16" t="e">
+        <f>$B$14/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"抖音来客",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="16" t="e">
+        <f>$B$15/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"微信堂食",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="16" t="e">
+        <f>$B$16/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"支付宝堂食",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="e">
+        <f>$B$17/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14">
+        <f>SUMIF(收入明细260410_1220131517[分类],"京东外卖",收入明细260410_1220131517[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="16" t="e">
+        <f>$B$18/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="21">
+        <f>SUM(B13:B18)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="22" t="e">
+        <f>SUM($C$13:$C$18)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A20" s="23"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A21" s="23"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="16">
+        <f>$B$24/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"工资",支出明细26049_1119141618[支出明细])</f>
+        <v>8500</v>
+      </c>
+      <c r="C25" s="16">
+        <f>$B$25/$B$4</f>
+        <v>0.536853407440157</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"房租",支出明细26049_1119141618[支出明细])</f>
+        <v>4333</v>
+      </c>
+      <c r="C26" s="16">
+        <f>$B$26/$B$4</f>
+        <v>0.27366891934567</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"推广",支出明细26049_1119141618[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="16">
+        <f>$B$27/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"水电",支出明细26049_1119141618[支出明细])</f>
+        <v>3000</v>
+      </c>
+      <c r="C28" s="16">
+        <f>$B$28/$B$4</f>
+        <v>0.189477673214173</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="14">
+        <f>SUMIF(支出明细26049_1119141618[分类],"其他",支出明细26049_1119141618[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="16">
+        <f>$B$29/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="30">
+        <f>SUM(B24:B29)</f>
+        <v>15833</v>
+      </c>
+      <c r="C30" s="31">
+        <f>SUM($C$24:$C$29)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="34">
+        <v>0</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="34">
+        <v>0</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="34">
+        <v>0</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="33"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="34">
+        <v>0</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="34">
+        <v>0</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="33"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="34">
+        <v>0</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="33"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="36"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:3">
+      <c r="B41" s="35"/>
+      <c r="C41" s="37"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:3">
+      <c r="B42" s="35"/>
+      <c r="C42" s="37"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="1">
+        <v>4333</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:3">
+      <c r="A45" s="1">
+        <v>8500</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="1">
+        <v>3000</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B2:B7 B44:B46">
+      <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
@@ -7542,7 +8071,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -7586,7 +8115,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_111914[支出明细])</f>
-        <v>30766.17</v>
+        <v>32589.93</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -7598,7 +8127,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_111914[分类],"食材",支出明细26049_111914[支出明细])</f>
-        <v>-11433.17</v>
+        <v>-16737.87</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -7610,7 +8139,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-30766.17</v>
+        <v>-32589.93</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -7783,11 +8312,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_111914[分类],"食材",支出明细26049_111914[支出明细])</f>
-        <v>11433.17</v>
+        <v>16737.87</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.37161499140127</v>
+        <v>0.51359024091184</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -7796,11 +8325,11 @@
       </c>
       <c r="B25" s="14">
         <f>SUMIF(支出明细26049_111914[分类],"工资",支出明细26049_111914[支出明细])</f>
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.390038799109541</v>
+        <v>0.260816761496573</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -7813,7 +8342,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.140836509711804</v>
+        <v>0.132955179713488</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -7822,11 +8351,11 @@
       </c>
       <c r="B27" s="14">
         <f>SUMIF(支出明细26049_111914[分类],"推广",支出明细26049_111914[支出明细])</f>
-        <v>0</v>
+        <v>19.06</v>
       </c>
       <c r="C27" s="16">
         <f>$B$27/$B$4</f>
-        <v>0</v>
+        <v>0.000584843232249962</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
@@ -7839,7 +8368,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.0975096997773854</v>
+        <v>0.0920529746458492</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -7861,7 +8390,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>30766.17</v>
+        <v>32589.93</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -7978,7 +8507,7 @@
     </row>
     <row r="45" customHeight="1" spans="1:3">
       <c r="A45" s="1">
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="B45" s="33" t="s">
         <v>68</v>
@@ -8073,6 +8602,94 @@
       </c>
       <c r="C53" s="2" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:3">
+      <c r="A54" s="1">
+        <v>4470</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:3">
+      <c r="A55" s="1">
+        <v>277.25</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:3">
+      <c r="A56" s="1">
+        <v>19.06</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:3">
+      <c r="A57" s="1">
+        <v>29</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:3">
+      <c r="A58" s="1">
+        <v>42</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:3">
+      <c r="A59" s="1">
+        <v>364.35</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:3">
+      <c r="A60" s="1">
+        <v>56</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:3">
+      <c r="A61" s="1">
+        <v>66.1</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -8083,7 +8700,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B2:B7 B44:B46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B2:B7 B44:B46">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8102,7 +8719,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -8146,7 +8763,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>19333</v>
+        <v>17503.7</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8158,7 +8775,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>0</v>
+        <v>-1670.7</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8170,7 +8787,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-19333</v>
+        <v>-17503.7</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8343,11 +8960,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>0</v>
+        <v>1670.7</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0</v>
+        <v>0.0954483909116358</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8356,11 +8973,11 @@
       </c>
       <c r="B25" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"工资",支出明细26049_11191416[支出明细])</f>
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.620700356902705</v>
+        <v>0.485611613544565</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -8373,7 +8990,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.224124553871618</v>
+        <v>0.2475476613516</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -8399,7 +9016,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.155175089225676</v>
+        <v>0.171392334192199</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -8421,7 +9038,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>19333</v>
+        <v>17503.7</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -8538,7 +9155,7 @@
     </row>
     <row r="45" customHeight="1" spans="1:3">
       <c r="A45" s="1">
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="B45" s="33" t="s">
         <v>68</v>
@@ -8556,6 +9173,39 @@
       </c>
       <c r="C46" s="33" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="1">
+        <v>589</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:3">
+      <c r="A49" s="1">
+        <v>81.7</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15220" tabRatio="723" firstSheet="1" activeTab="7"/>
+    <workbookView windowHeight="15820" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15820" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15820" tabRatio="723" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -681,13 +681,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -737,10 +737,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -762,14 +785,74 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -788,89 +871,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -949,7 +949,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -961,61 +1099,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1027,67 +1111,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1099,31 +1123,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1202,61 +1202,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1278,6 +1224,54 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1287,303 +1281,309 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1664,13 +1664,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1685,7 +1685,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1750,7 +1750,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_122013[收入明细])</f>
-        <v>0</v>
+        <v>32428.22</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_111914[分类],"食材",支出明细26049_111914[支出明细])</f>
-        <v>-16737.87</v>
+        <v>15690.35</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-32589.93</v>
+        <v>-161.710000000003</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8149,9 +8149,9 @@
       <c r="A7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="16" t="e">
+      <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.483848635540279</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8161,9 +8161,9 @@
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="16" t="e">
+      <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>-0.00498670602333408</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8201,11 +8201,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"淘宝外卖",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16" t="e">
+        <v>13210.51</v>
+      </c>
+      <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.407376969812096</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8214,11 +8214,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"美团外卖",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="16" t="e">
+        <v>12995.5</v>
+      </c>
+      <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.400746633641933</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8227,11 +8227,11 @@
       </c>
       <c r="B15" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"抖音来客",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C15" s="16" t="e">
+        <v>34.62</v>
+      </c>
+      <c r="C15" s="16">
         <f>$B$15/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.00106758866197405</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -8240,11 +8240,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"微信堂食",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="16" t="e">
+        <v>2908</v>
+      </c>
+      <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0896749806187327</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8253,11 +8253,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"支付宝堂食",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="e">
+        <v>1333.65</v>
+      </c>
+      <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0411262166101007</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8266,11 +8266,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"京东外卖",收入明细260410_122013[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="e">
+        <v>1945.94</v>
+      </c>
+      <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0600076106551639</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8279,11 +8279,11 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="22" t="e">
+        <v>32428.22</v>
+      </c>
+      <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="1" customHeight="1" spans="1:1">
@@ -8410,7 +8410,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>0</v>
+        <v>2723</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="34">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>62</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>0</v>
+        <v>1333.65</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>0</v>
+        <v>1945.94</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>0</v>
+        <v>13210.51</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -8459,7 +8459,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>0</v>
+        <v>12995.5</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="1">
-        <v>0</v>
+        <v>34.62</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>135</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -681,13 +681,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -731,118 +731,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -860,7 +754,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -871,6 +787,90 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -949,7 +949,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -961,19 +1063,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,43 +1075,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1033,31 +1099,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1069,61 +1117,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1201,47 +1201,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1270,12 +1231,25 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1295,294 +1269,320 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1664,15 +1664,15 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1685,7 +1685,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1750,7 +1750,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_122013[收入明细])</f>
-        <v>32428.22</v>
+        <v>34107.25</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_111914[分类],"食材",支出明细26049_111914[支出明细])</f>
-        <v>15690.35</v>
+        <v>17369.38</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8139,7 +8139,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-161.710000000003</v>
+        <v>1517.32</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.483848635540279</v>
+        <v>0.509257709138087</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>-0.00498670602333408</v>
+        <v>0.0444867293610596</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8201,11 +8201,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"淘宝外卖",收入明细260410_122013[收入明细])</f>
-        <v>13210.51</v>
+        <v>13553</v>
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.407376969812096</v>
+        <v>0.397364196761686</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8214,11 +8214,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"美团外卖",收入明细260410_122013[收入明细])</f>
-        <v>12995.5</v>
+        <v>13435.44</v>
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.400746633641933</v>
+        <v>0.393917422248935</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8227,11 +8227,11 @@
       </c>
       <c r="B15" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"抖音来客",收入明细260410_122013[收入明细])</f>
-        <v>34.62</v>
+        <v>80.35</v>
       </c>
       <c r="C15" s="16">
         <f>$B$15/$B$3</f>
-        <v>0.00106758866197405</v>
+        <v>0.00235580411789282</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -8240,11 +8240,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"微信堂食",收入明细260410_122013[收入明细])</f>
-        <v>2908</v>
+        <v>3340.7</v>
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0896749806187327</v>
+        <v>0.0979469174442384</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8253,11 +8253,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"支付宝堂食",收入明细260410_122013[收入明细])</f>
-        <v>1333.65</v>
+        <v>1709.88</v>
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.0411262166101007</v>
+        <v>0.0501324498457073</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8266,11 +8266,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_122013[分类],"京东外卖",收入明细260410_122013[收入明细])</f>
-        <v>1945.94</v>
+        <v>1987.88</v>
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0600076106551639</v>
+        <v>0.0582832095815406</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>32428.22</v>
+        <v>34107.25</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>2723</v>
+        <v>2791.82</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="34">
-        <v>185</v>
+        <v>548.88</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>62</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>1333.65</v>
+        <v>1709.88</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -8441,7 +8441,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>1945.94</v>
+        <v>1987.88</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -8450,7 +8450,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>13210.51</v>
+        <v>13553</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -8459,7 +8459,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>12995.5</v>
+        <v>13435.44</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>
@@ -8468,7 +8468,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="1">
-        <v>34.62</v>
+        <v>80.35</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>135</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15820" tabRatio="723" firstSheet="1" activeTab="7"/>
+    <workbookView windowHeight="15360" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="220">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -674,6 +674,15 @@
   </si>
   <si>
     <t>烧麦</t>
+  </si>
+  <si>
+    <t>拼多多肉片</t>
+  </si>
+  <si>
+    <t>王道凯肉片</t>
+  </si>
+  <si>
+    <t>牛肉酱一瓶</t>
   </si>
 </sst>
 </file>
@@ -682,11 +691,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
@@ -744,9 +753,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -768,48 +776,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -829,15 +799,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -852,23 +816,68 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -949,7 +958,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -961,13 +988,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,79 +1018,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1069,13 +1036,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1087,31 +1066,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1124,6 +1091,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1216,36 +1225,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1270,6 +1249,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1281,6 +1275,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1298,142 +1307,142 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1891,8 +1900,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C52">
-  <autoFilter ref="A43:C52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C56">
+  <autoFilter ref="A43:C56"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
     <tableColumn id="2" name="分类"/>
@@ -8115,7 +8124,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_111914[支出明细])</f>
-        <v>32589.93</v>
+        <v>32522.33</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8139,7 +8148,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>1517.32</v>
+        <v>1584.92</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8163,7 +8172,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>0.0444867293610596</v>
+        <v>0.0464687126637299</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8316,7 +8325,7 @@
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.51359024091184</v>
+        <v>0.514657775134807</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8325,11 +8334,11 @@
       </c>
       <c r="B25" s="14">
         <f>SUMIF(支出明细26049_111914[分类],"工资",支出明细26049_111914[支出明细])</f>
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.260816761496573</v>
+        <v>0.276732940106075</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -8342,7 +8351,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.132955179713488</v>
+        <v>0.133231536608847</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -8355,7 +8364,7 @@
       </c>
       <c r="C27" s="16">
         <f>$B$27/$B$4</f>
-        <v>0.000584843232249962</v>
+        <v>0.000586058870935754</v>
       </c>
     </row>
     <row r="28" customHeight="1" spans="1:3">
@@ -8364,11 +8373,11 @@
       </c>
       <c r="B28" s="14">
         <f>SUMIF(支出明细26049_111914[分类],"水电",支出明细26049_111914[支出明细])</f>
-        <v>3000</v>
+        <v>2432.4</v>
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.0920529746458492</v>
+        <v>0.0747916892793352</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -8390,7 +8399,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>32589.93</v>
+        <v>32522.33</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -8507,24 +8516,24 @@
     </row>
     <row r="45" customHeight="1" spans="1:3">
       <c r="A45" s="1">
-        <v>8500</v>
+        <v>9000</v>
       </c>
       <c r="B45" s="33" t="s">
         <v>68</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="1">
-        <v>3000</v>
+        <v>2432.4</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:3">
@@ -8719,7 +8728,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -8763,7 +8772,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>17503.7</v>
+        <v>26418.34</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8775,7 +8784,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>-1670.7</v>
+        <v>-10585.34</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8787,7 +8796,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-17503.7</v>
+        <v>-26418.34</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8960,11 +8969,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>1670.7</v>
+        <v>10585.34</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.0954483909116358</v>
+        <v>0.40068149626358</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8977,7 +8986,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.485611613544565</v>
+        <v>0.321746180872833</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -8990,7 +8999,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.2475476613516</v>
+        <v>0.16401484726141</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -9016,7 +9025,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.171392334192199</v>
+        <v>0.113557475602176</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -9038,7 +9047,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>17503.7</v>
+        <v>26418.34</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -9206,6 +9215,83 @@
       </c>
       <c r="C49" s="2" t="s">
         <v>216</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:3">
+      <c r="A50" s="1">
+        <v>263.64</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:3">
+      <c r="A51" s="1">
+        <v>6192</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:3">
+      <c r="A52" s="1">
+        <v>12.9</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:3">
+      <c r="A53" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:3">
+      <c r="A54" s="1">
+        <v>593.8</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:3">
+      <c r="A55" s="1">
+        <v>81.3</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:3">
+      <c r="A56" s="1">
+        <v>771</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -9216,7 +9302,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B2:B7 B44:B46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B2:B7 B44:B46">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8760,7 +8760,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
+        <v>15759.92</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8772,7 +8772,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>26418.34</v>
+        <v>25918.34</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>-10585.34</v>
+        <v>5174.58</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-26418.34</v>
+        <v>-10158.42</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8806,9 +8806,9 @@
       <c r="A7" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="16" t="e">
+      <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.328337961106402</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8818,9 +8818,9 @@
       <c r="A8" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="16" t="e">
+      <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>-0.644573068898827</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8858,11 +8858,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"淘宝外卖",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C13" s="16" t="e">
+        <v>7269.78</v>
+      </c>
+      <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.46128279838984</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8871,11 +8871,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"美团外卖",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C14" s="16" t="e">
+        <v>5646.74</v>
+      </c>
+      <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.358297504048244</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8886,9 +8886,9 @@
         <f>SUMIF(收入明细260410_12201315[分类],"抖音来客",收入明细260410_12201315[收入明细])</f>
         <v>0</v>
       </c>
-      <c r="C15" s="16" t="e">
+      <c r="C15" s="16">
         <f>$B$15/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -8897,11 +8897,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"微信堂食",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="16" t="e">
+        <v>1186.18</v>
+      </c>
+      <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0752656104853324</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8910,11 +8910,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"支付宝堂食",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="16" t="e">
+        <v>1259.39</v>
+      </c>
+      <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0799109386342063</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8923,11 +8923,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"京东外卖",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
-      </c>
-      <c r="C18" s="16" t="e">
+        <v>397.83</v>
+      </c>
+      <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>#DIV/0!</v>
+        <v>0.0252431484423779</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8936,11 +8936,11 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="22" t="e">
+        <v>15759.92</v>
+      </c>
+      <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" customFormat="1" customHeight="1" spans="1:1">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.40068149626358</v>
+        <v>0.408411186827551</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.321746180872833</v>
+        <v>0.327953101934769</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.16401484726141</v>
+        <v>0.167178916550983</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -9021,11 +9021,11 @@
       </c>
       <c r="B28" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"水电",支出明细26049_11191416[支出明细])</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.113557475602176</v>
+        <v>0.0964567946866968</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>26418.34</v>
+        <v>25918.34</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -9067,7 +9067,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>0</v>
+        <v>114.95</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -9078,7 +9078,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="34">
-        <v>0</v>
+        <v>1071.23</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>62</v>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>0</v>
+        <v>1259.39</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -9098,7 +9098,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>0</v>
+        <v>397.83</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -9107,7 +9107,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>0</v>
+        <v>7269.78</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -9116,7 +9116,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>0</v>
+        <v>5646.74</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>
@@ -9175,7 +9175,7 @@
     </row>
     <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>37</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="16120" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="997" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="221">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -683,6 +683,9 @@
   </si>
   <si>
     <t>牛肉酱一瓶</t>
+  </si>
+  <si>
+    <t>老池垫付</t>
   </si>
 </sst>
 </file>
@@ -690,13 +693,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -740,13 +743,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -760,8 +756,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -776,15 +779,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -807,18 +802,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -830,8 +825,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -845,17 +855,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -863,21 +864,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -952,7 +955,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -964,25 +1009,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -994,7 +1033,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1006,127 +1123,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1210,24 +1213,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -1265,6 +1250,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1279,17 +1279,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1307,292 +1310,292 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="39" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1673,13 +1676,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1694,7 +1697,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1759,7 +1762,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -1900,8 +1903,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C56">
-  <autoFilter ref="A43:C56"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C61">
+  <autoFilter ref="A43:C61"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
     <tableColumn id="2" name="分类"/>
@@ -8728,7 +8731,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -8760,7 +8763,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>15759.92</v>
+        <v>23821.19</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8772,7 +8775,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>25918.34</v>
+        <v>34486.34</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8784,7 +8787,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>5174.58</v>
+        <v>4667.85000000001</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8796,7 +8799,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-10158.42</v>
+        <v>-10665.15</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8808,7 +8811,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.328337961106402</v>
+        <v>0.195953686612634</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8820,7 +8823,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>-0.644573068898827</v>
+        <v>-0.447716927659785</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8858,11 +8861,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"淘宝外卖",收入明细260410_12201315[收入明细])</f>
-        <v>7269.78</v>
+        <v>10861.96</v>
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.46128279838984</v>
+        <v>0.455978899458843</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8871,11 +8874,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"美团外卖",收入明细260410_12201315[收入明细])</f>
-        <v>5646.74</v>
+        <v>8727.69</v>
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.358297504048244</v>
+        <v>0.366383459432547</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8897,11 +8900,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"微信堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1186.18</v>
+        <v>1937.45</v>
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0752656104853324</v>
+        <v>0.0813330484329288</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8910,11 +8913,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"支付宝堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1259.39</v>
+        <v>1505.8</v>
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.0799109386342063</v>
+        <v>0.0632126270769848</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8923,11 +8926,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"京东外卖",收入明细260410_12201315[收入明细])</f>
-        <v>397.83</v>
+        <v>788.29</v>
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0252431484423779</v>
+        <v>0.0330919655986959</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8936,7 +8939,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>15759.92</v>
+        <v>23821.19</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -8969,11 +8972,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>10585.34</v>
+        <v>19153.34</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.408411186827551</v>
+        <v>0.555389177280048</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8986,7 +8989,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.327953101934769</v>
+        <v>0.246474401168695</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -8999,7 +9002,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.167178916550983</v>
+        <v>0.125643950619289</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -9025,7 +9028,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.0964567946866968</v>
+        <v>0.072492470931969</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -9047,7 +9050,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>25918.34</v>
+        <v>34486.34</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -9067,7 +9070,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>114.95</v>
+        <v>1790.5</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -9078,7 +9081,7 @@
     </row>
     <row r="35" customHeight="1" spans="1:3">
       <c r="A35" s="34">
-        <v>1071.23</v>
+        <v>146.95</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>62</v>
@@ -9089,7 +9092,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>1259.39</v>
+        <v>1505.8</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -9098,7 +9101,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>397.83</v>
+        <v>788.29</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -9107,7 +9110,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>7269.78</v>
+        <v>10861.96</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -9116,7 +9119,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>5646.74</v>
+        <v>8727.69</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>
@@ -9292,6 +9295,61 @@
       </c>
       <c r="C56" s="2" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:3">
+      <c r="A57" s="1">
+        <v>885</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:3">
+      <c r="A58" s="1">
+        <v>805</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:3">
+      <c r="A59" s="1">
+        <v>300</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:3">
+      <c r="A60" s="1">
+        <v>5578</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:3">
+      <c r="A61" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -9302,7 +9360,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B2:B7 B44:B46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B2:B7 B44:B46">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16120" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15360" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -693,13 +693,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
+    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -743,6 +743,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -756,18 +763,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -778,11 +778,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -802,8 +825,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -817,24 +857,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -847,34 +871,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -955,13 +955,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -973,7 +967,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,7 +979,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,31 +1021,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1039,19 +1039,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1063,7 +1057,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,31 +1093,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1111,31 +1117,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,8 +1213,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1249,17 +1273,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1281,24 +1299,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1310,255 +1310,255 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="35" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1568,13 +1568,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1676,7 +1676,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>23821.19</v>
+        <v>28485.37</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>4667.85000000001</v>
+        <v>9332.03</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-10665.15</v>
+        <v>-6000.97</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.195953686612634</v>
+        <v>0.327607821137658</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>-0.447716927659785</v>
+        <v>-0.210668494037466</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8861,11 +8861,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"淘宝外卖",收入明细260410_12201315[收入明细])</f>
-        <v>10861.96</v>
+        <v>12943.59</v>
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.455978899458843</v>
+        <v>0.454394308376546</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8874,11 +8874,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"美团外卖",收入明细260410_12201315[收入明细])</f>
-        <v>8727.69</v>
+        <v>10711.38</v>
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.366383459432547</v>
+        <v>0.376030923944467</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8900,11 +8900,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"微信堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1937.45</v>
+        <v>2319.88</v>
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0813330484329288</v>
+        <v>0.0814411046793494</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8913,11 +8913,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"支付宝堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1505.8</v>
+        <v>1632.8</v>
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.0632126270769848</v>
+        <v>0.0573206526718803</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"京东外卖",收入明细260410_12201315[收入明细])</f>
-        <v>788.29</v>
+        <v>877.72</v>
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0330919655986959</v>
+        <v>0.0308130103277577</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>23821.19</v>
+        <v>28485.37</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>1790.5</v>
+        <v>2172.93</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>1505.8</v>
+        <v>1632.8</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>788.29</v>
+        <v>877.72</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>10861.96</v>
+        <v>12943.59</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>8727.69</v>
+        <v>10711.38</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15360" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15440" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -693,13 +693,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="177" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -743,14 +743,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -763,18 +772,40 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -788,14 +819,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -817,33 +841,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -858,7 +865,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -871,16 +878,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -961,13 +961,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -979,19 +973,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1003,19 +991,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1027,19 +1027,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1057,13 +1045,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,7 +1087,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1087,55 +1129,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,8 +1213,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1230,15 +1259,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1273,15 +1293,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1296,269 +1307,258 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1568,13 +1568,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1676,7 +1676,7 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>28485.37</v>
+        <v>34965.78</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>9332.03</v>
+        <v>15812.44</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-6000.97</v>
+        <v>479.440000000002</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.327607821137658</v>
+        <v>0.452226147965239</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>-0.210668494037466</v>
+        <v>0.0137116918312705</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8861,11 +8861,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"淘宝外卖",收入明细260410_12201315[收入明细])</f>
-        <v>12943.59</v>
+        <v>15876.72</v>
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.454394308376546</v>
+        <v>0.454064516793276</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8874,11 +8874,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"美团外卖",收入明细260410_12201315[收入明细])</f>
-        <v>10711.38</v>
+        <v>13272.66</v>
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.376030923944467</v>
+        <v>0.379589987696542</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8900,11 +8900,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"微信堂食",收入明细260410_12201315[收入明细])</f>
-        <v>2319.88</v>
+        <v>2742.61</v>
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0814411046793494</v>
+        <v>0.0784369746649438</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8913,11 +8913,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"支付宝堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1632.8</v>
+        <v>1997.6</v>
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.0573206526718803</v>
+        <v>0.05713014267092</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"京东外卖",收入明细260410_12201315[收入明细])</f>
-        <v>877.72</v>
+        <v>1076.19</v>
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0308130103277577</v>
+        <v>0.0307783781743179</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>28485.37</v>
+        <v>34965.78</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>2172.93</v>
+        <v>2595.66</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>1632.8</v>
+        <v>1997.6</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>877.72</v>
+        <v>1076.19</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>12943.59</v>
+        <v>15876.72</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>10711.38</v>
+        <v>13272.66</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>34965.78</v>
+        <v>35000.78</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>15812.44</v>
+        <v>15847.44</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>479.440000000002</v>
+        <v>514.440000000002</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.452226147965239</v>
+        <v>0.452773909610015</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>0.0137116918312705</v>
+        <v>0.0146979581597896</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8865,7 +8865,7 @@
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.454064516793276</v>
+        <v>0.453610462395409</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.379589987696542</v>
+        <v>0.379210406168091</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8887,11 +8887,11 @@
       </c>
       <c r="B15" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"抖音来客",收入明细260410_12201315[收入明细])</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C15" s="16">
         <f>$B$15/$B$3</f>
-        <v>0</v>
+        <v>0.000999977714782356</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0784369746649438</v>
+        <v>0.0783585394382639</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.05713014267092</v>
+        <v>0.0570730138014067</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0307783781743179</v>
+        <v>0.0307476004820464</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>34965.78</v>
+        <v>35000.78</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="1">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>135</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15440" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15300" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -693,13 +693,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -743,9 +743,24 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -754,14 +769,6 @@
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -779,30 +786,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -812,14 +797,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -835,7 +812,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -849,23 +834,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -878,9 +856,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -961,6 +961,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -973,7 +979,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,7 +1003,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,37 +1111,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1039,103 +1129,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,8 +1213,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1223,26 +1223,6 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1263,21 +1243,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1289,6 +1254,17 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1307,151 +1283,175 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="32" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1556,45 +1556,45 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1676,15 +1676,15 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1697,7 +1697,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1762,7 +1762,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="B3" s="8">
         <f>SUM(收入明细260410_12201315[收入明细])</f>
-        <v>35000.78</v>
+        <v>36923.89</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>49</v>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>15847.44</v>
+        <v>17770.55</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>514.440000000002</v>
+        <v>2437.55</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.452773909610015</v>
+        <v>0.481275131087218</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>0.0146979581597896</v>
+        <v>0.0660155254497834</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8861,11 +8861,11 @@
       </c>
       <c r="B13" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"淘宝外卖",收入明细260410_12201315[收入明细])</f>
-        <v>15876.72</v>
+        <v>16613.36</v>
       </c>
       <c r="C13" s="16">
         <f>$B$13/$B$3</f>
-        <v>0.453610462395409</v>
+        <v>0.449935258717324</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:3">
@@ -8874,11 +8874,11 @@
       </c>
       <c r="B14" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"美团外卖",收入明细260410_12201315[收入明细])</f>
-        <v>13272.66</v>
+        <v>14177.95</v>
       </c>
       <c r="C14" s="16">
         <f>$B$14/$B$3</f>
-        <v>0.379210406168091</v>
+        <v>0.383977690324611</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:3">
@@ -8887,11 +8887,11 @@
       </c>
       <c r="B15" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"抖音来客",收入明细260410_12201315[收入明细])</f>
-        <v>35</v>
+        <v>40.11</v>
       </c>
       <c r="C15" s="16">
         <f>$B$15/$B$3</f>
-        <v>0.000999977714782356</v>
+        <v>0.00108628857902025</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="1:3">
@@ -8900,11 +8900,11 @@
       </c>
       <c r="B16" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"微信堂食",收入明细260410_12201315[收入明细])</f>
-        <v>2742.61</v>
+        <v>2839.61</v>
       </c>
       <c r="C16" s="16">
         <f>$B$16/$B$3</f>
-        <v>0.0783585394382639</v>
+        <v>0.0769044106674567</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:3">
@@ -8913,11 +8913,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"支付宝堂食",收入明细260410_12201315[收入明细])</f>
-        <v>1997.6</v>
+        <v>2057.57</v>
       </c>
       <c r="C17" s="16">
         <f>$B$17/$B$3</f>
-        <v>0.0570730138014067</v>
+        <v>0.0557246270639415</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:3">
@@ -8926,11 +8926,11 @@
       </c>
       <c r="B18" s="14">
         <f>SUMIF(收入明细260410_12201315[分类],"京东外卖",收入明细260410_12201315[收入明细])</f>
-        <v>1076.19</v>
+        <v>1195.29</v>
       </c>
       <c r="C18" s="16">
         <f>$B$18/$B$3</f>
-        <v>0.0307476004820464</v>
+        <v>0.0323717246476468</v>
       </c>
     </row>
     <row r="19" customHeight="1" spans="1:3">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="B19" s="21">
         <f>SUM(B13:B18)</f>
-        <v>35000.78</v>
+        <v>36923.89</v>
       </c>
       <c r="C19" s="22">
         <f>SUM($C$13:$C$18)</f>
@@ -9070,7 +9070,7 @@
     </row>
     <row r="34" customHeight="1" spans="1:3">
       <c r="A34" s="34">
-        <v>2595.66</v>
+        <v>2692.66</v>
       </c>
       <c r="B34" s="32" t="s">
         <v>62</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="36" customHeight="1" spans="1:3">
       <c r="A36" s="34">
-        <v>1997.6</v>
+        <v>2057.57</v>
       </c>
       <c r="B36" s="32" t="s">
         <v>63</v>
@@ -9101,7 +9101,7 @@
     </row>
     <row r="37" customHeight="1" spans="1:3">
       <c r="A37" s="34">
-        <v>1076.19</v>
+        <v>1195.29</v>
       </c>
       <c r="B37" s="32" t="s">
         <v>64</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="38" customHeight="1" spans="1:3">
       <c r="A38" s="34">
-        <v>15876.72</v>
+        <v>16613.36</v>
       </c>
       <c r="B38" s="32" t="s">
         <v>60</v>
@@ -9119,7 +9119,7 @@
     </row>
     <row r="39" customHeight="1" spans="1:3">
       <c r="A39" s="34">
-        <v>13272.66</v>
+        <v>14177.95</v>
       </c>
       <c r="B39" s="32" t="s">
         <v>61</v>
@@ -9128,7 +9128,7 @@
     </row>
     <row r="40" customHeight="1" spans="1:3">
       <c r="A40" s="1">
-        <v>35</v>
+        <v>40.11</v>
       </c>
       <c r="B40" s="35" t="s">
         <v>135</v>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="223">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -686,6 +686,12 @@
   </si>
   <si>
     <t>老池垫付</t>
+  </si>
+  <si>
+    <t>香菜</t>
+  </si>
+  <si>
+    <t>酸笋</t>
   </si>
 </sst>
 </file>
@@ -1903,8 +1909,8 @@
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C61">
-  <autoFilter ref="A43:C61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="支出明细26049_11191416" displayName="支出明细26049_11191416" ref="A43:C62">
+  <autoFilter ref="A43:C62"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
     <tableColumn id="2" name="分类"/>
@@ -2822,7 +2828,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -2866,7 +2872,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_1119141618[支出明细])</f>
-        <v>15833</v>
+        <v>23549.5</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -2878,7 +2884,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
-        <v>0</v>
+        <v>-7716.5</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -2890,7 +2896,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-15833</v>
+        <v>-23549.5</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -3063,11 +3069,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
-        <v>0</v>
+        <v>7716.5</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0</v>
+        <v>0.327671500456485</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -3080,7 +3086,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.536853407440157</v>
+        <v>0.360941845899064</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -3093,7 +3099,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.27366891934567</v>
+        <v>0.18399541391537</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -3119,7 +3125,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.189477673214173</v>
+        <v>0.127391239729081</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -3141,7 +3147,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>15833</v>
+        <v>23549.5</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -3276,6 +3282,61 @@
       </c>
       <c r="C46" s="33" t="s">
         <v>160</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:3">
+      <c r="A47" s="1">
+        <v>272.2</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:3">
+      <c r="A48" s="1">
+        <v>6182</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:3">
+      <c r="A49" s="1">
+        <v>620</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:3">
+      <c r="A50" s="1">
+        <v>610.8</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:3">
+      <c r="A51" s="1">
+        <v>31.5</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -8731,7 +8792,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -8775,7 +8836,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>34486.34</v>
+        <v>34512.14</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8787,7 +8848,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>17770.55</v>
+        <v>17744.75</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -8799,7 +8860,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>2437.55</v>
+        <v>2411.75</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8811,7 +8872,7 @@
       </c>
       <c r="B7" s="16">
         <f>$B$5/$B$3</f>
-        <v>0.481275131087218</v>
+        <v>0.480576396473936</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>54</v>
@@ -8823,7 +8884,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>0.0660155254497834</v>
+        <v>0.0653167908365018</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -8972,11 +9033,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"食材",支出明细26049_11191416[支出明细])</f>
-        <v>19153.34</v>
+        <v>19179.14</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.555389177280048</v>
+        <v>0.555721551894493</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -8989,7 +9050,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.246474401168695</v>
+        <v>0.246290146018184</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -9002,7 +9063,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.125643950619289</v>
+        <v>0.125550023846681</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -9028,7 +9089,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.072492470931969</v>
+        <v>0.0724382782406423</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -9050,7 +9111,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>34486.34</v>
+        <v>34512.14</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -9350,6 +9411,17 @@
       </c>
       <c r="C61" s="2" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="62" customHeight="1" spans="1:3">
+      <c r="A62" s="1">
+        <v>25.8</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -9360,7 +9432,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B2:B7 B44:B46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B54 B55 B56 B57 B58 B59 B60 B61 B62 B2:B7 B44:B46">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15300" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15900" tabRatio="723" firstSheet="1" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15900" tabRatio="723" firstSheet="1" activeTab="8"/>
+    <workbookView windowHeight="15220" tabRatio="723" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="224">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>火鸡面</t>
+  </si>
+  <si>
+    <t>水电费付</t>
   </si>
   <si>
     <t>快驴</t>
@@ -699,13 +702,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="0.00_ ;[Red]\-0.00\ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="0.00_ ;[Red]\-0.00\ "/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -763,14 +766,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
@@ -785,6 +780,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
@@ -792,17 +795,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -817,6 +820,14 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
@@ -824,9 +835,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -840,30 +858,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -885,8 +881,15 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -967,12 +970,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -985,7 +982,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,43 +1114,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1045,103 +1144,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1229,7 +1232,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1245,6 +1248,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1276,6 +1288,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1289,169 +1316,145 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="41" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1463,145 +1466,145 @@
   </cellStyleXfs>
   <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1682,13 +1685,13 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1703,7 +1706,7 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1768,7 +1771,7 @@
         <sz val="11"/>
         <color theme="1"/>
       </font>
-      <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
+      <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
     </dxf>
     <dxf>
       <font>
@@ -3336,7 +3339,7 @@
         <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -8836,7 +8839,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_11191416[支出明细])</f>
-        <v>34512.14</v>
+        <v>34304.54</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -8860,7 +8863,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>2411.75</v>
+        <v>2619.34999999999</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -8884,7 +8887,7 @@
       </c>
       <c r="B8" s="16">
         <f>$B$6/$B$3</f>
-        <v>0.0653167908365018</v>
+        <v>0.0709391670270925</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>54</v>
@@ -9037,7 +9040,7 @@
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.555721551894493</v>
+        <v>0.559084599297935</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -9050,7 +9053,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.246290146018184</v>
+        <v>0.247780614460943</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -9063,7 +9066,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.125550023846681</v>
+        <v>0.126309812054031</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -9085,11 +9088,11 @@
       </c>
       <c r="B28" s="14">
         <f>SUMIF(支出明细26049_11191416[分类],"水电",支出明细26049_11191416[支出明细])</f>
-        <v>2500</v>
+        <v>2292.4</v>
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.0724382782406423</v>
+        <v>0.0668249741870901</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -9111,7 +9114,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>34512.14</v>
+        <v>34304.54</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -9234,18 +9237,18 @@
         <v>68</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>160</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="1">
-        <v>2500</v>
+        <v>2292.4</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>37</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>160</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" customHeight="1" spans="1:3">
@@ -9267,7 +9270,7 @@
         <v>25</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="49" customHeight="1" spans="1:3">
@@ -9278,7 +9281,7 @@
         <v>25</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" customHeight="1" spans="1:3">
@@ -9289,7 +9292,7 @@
         <v>25</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="51" customHeight="1" spans="1:3">
@@ -9300,7 +9303,7 @@
         <v>25</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="52" customHeight="1" spans="1:3">
@@ -9311,7 +9314,7 @@
         <v>25</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="53" customHeight="1" spans="1:3">
@@ -9388,7 +9391,7 @@
         <v>25</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" customHeight="1" spans="1:3">
@@ -9421,7 +9424,7 @@
         <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15220" tabRatio="723" activeTab="8"/>
+    <workbookView windowHeight="15220" tabRatio="723" firstSheet="2" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -17,13 +17,14 @@
     <sheet name="2026-08流水" sheetId="8" r:id="rId8"/>
     <sheet name="2026-09流水" sheetId="9" r:id="rId9"/>
     <sheet name="2026-10流水" sheetId="10" r:id="rId10"/>
+    <sheet name="2026-11流水" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="224">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -1959,6 +1960,30 @@
 </table>
 </file>
 
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="收入明细260410_122013151721" displayName="收入明细260410_122013151721" ref="A33:C40">
+  <autoFilter ref="A33:C40"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="收入明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="支出明细26049_111914161822" displayName="支出明细26049_111914161822" ref="A43:C52">
+  <autoFilter ref="A43:C52"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="支出明细"/>
+    <tableColumn id="2" name="分类"/>
+    <tableColumn id="3" name="说明"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="支出明细2602" displayName="支出明细2602" ref="A40:C60" totalsRowShown="0">
   <autoFilter ref="A40:C60"/>
@@ -2875,7 +2900,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_1119141618[支出明细])</f>
-        <v>23549.5</v>
+        <v>23049.5</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -2899,7 +2924,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-23549.5</v>
+        <v>-23049.5</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -3076,7 +3101,7 @@
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.327671500456485</v>
+        <v>0.334779496301438</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -3089,7 +3114,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.360941845899064</v>
+        <v>0.368771556866743</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -3102,7 +3127,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.18399541391537</v>
+        <v>0.187986724223953</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -3124,11 +3149,11 @@
       </c>
       <c r="B28" s="14">
         <f>SUMIF(支出明细26049_1119141618[分类],"水电",支出明细26049_1119141618[支出明细])</f>
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.127391239729081</v>
+        <v>0.108462222607866</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -3150,7 +3175,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>23549.5</v>
+        <v>23049.5</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -3278,7 +3303,7 @@
     </row>
     <row r="46" customHeight="1" spans="1:3">
       <c r="A46" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="B46" s="33" t="s">
         <v>37</v>
@@ -3340,6 +3365,489 @@
       </c>
       <c r="C51" s="2" t="s">
         <v>223</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:C23"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B2:B7 B44:B46">
+      <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:C46"/>
+  <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.625" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="30.625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" customHeight="1" spans="1:3">
+      <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+    </row>
+    <row r="2" customHeight="1" spans="1:3">
+      <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="1:3">
+      <c r="A3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="8">
+        <f>SUM(收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="1:3">
+      <c r="A4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="11">
+        <f>SUM(支出明细26049_111914161822[支出明细])</f>
+        <v>15333</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:3">
+      <c r="A5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="14">
+        <f>$B$3-SUMIF(支出明细26049_111914161822[分类],"食材",支出明细26049_111914161822[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:3">
+      <c r="A6" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="14">
+        <f>$B$3-$B$4</f>
+        <v>-15333</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="16" t="e">
+        <f>$B$5/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="16" t="e">
+        <f>$B$6/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="2:3">
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+    </row>
+    <row r="10" customHeight="1" spans="2:3">
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+    </row>
+    <row r="11" customHeight="1" spans="1:3">
+      <c r="A11" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:3">
+      <c r="A12" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:3">
+      <c r="A13" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B13" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"淘宝外卖",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="16" t="e">
+        <f>$B$13/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:3">
+      <c r="A14" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"美团外卖",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C14" s="16" t="e">
+        <f>$B$14/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:3">
+      <c r="A15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="B15" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"抖音来客",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C15" s="16" t="e">
+        <f>$B$15/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:3">
+      <c r="A16" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"微信堂食",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C16" s="16" t="e">
+        <f>$B$16/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:3">
+      <c r="A17" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"支付宝堂食",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="16" t="e">
+        <f>$B$17/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:3">
+      <c r="A18" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="14">
+        <f>SUMIF(收入明细260410_122013151721[分类],"京东外卖",收入明细260410_122013151721[收入明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C18" s="16" t="e">
+        <f>$B$18/$B$3</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:3">
+      <c r="A19" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B19" s="21">
+        <f>SUM(B13:B18)</f>
+        <v>0</v>
+      </c>
+      <c r="C19" s="22" t="e">
+        <f>SUM($C$13:$C$18)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A20" s="23"/>
+    </row>
+    <row r="21" customFormat="1" customHeight="1" spans="1:1">
+      <c r="A21" s="23"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:3">
+      <c r="A22" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+    </row>
+    <row r="23" customHeight="1" spans="1:3">
+      <c r="A23" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="28"/>
+    </row>
+    <row r="24" customHeight="1" spans="1:3">
+      <c r="A24" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"食材",支出明细26049_111914161822[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C24" s="16">
+        <f>$B$24/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:3">
+      <c r="A25" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"工资",支出明细26049_111914161822[支出明细])</f>
+        <v>8500</v>
+      </c>
+      <c r="C25" s="16">
+        <f>$B$25/$B$4</f>
+        <v>0.554359877388639</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:3">
+      <c r="A26" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"房租",支出明细26049_111914161822[支出明细])</f>
+        <v>4333</v>
+      </c>
+      <c r="C26" s="16">
+        <f>$B$26/$B$4</f>
+        <v>0.282593099849997</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:3">
+      <c r="A27" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"推广",支出明细26049_111914161822[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C27" s="16">
+        <f>$B$27/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:3">
+      <c r="A28" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"水电",支出明细26049_111914161822[支出明细])</f>
+        <v>2500</v>
+      </c>
+      <c r="C28" s="16">
+        <f>$B$28/$B$4</f>
+        <v>0.163047022761364</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:3">
+      <c r="A29" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="14">
+        <f>SUMIF(支出明细26049_111914161822[分类],"其他",支出明细26049_111914161822[支出明细])</f>
+        <v>0</v>
+      </c>
+      <c r="C29" s="16">
+        <f>$B$29/$B$4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:3">
+      <c r="A30" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="30">
+        <f>SUM(B24:B29)</f>
+        <v>15333</v>
+      </c>
+      <c r="C30" s="31">
+        <f>SUM($C$24:$C$29)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:3">
+      <c r="A33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:3">
+      <c r="A34" s="34">
+        <v>0</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:3">
+      <c r="A35" s="34">
+        <v>0</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:3">
+      <c r="A36" s="34">
+        <v>0</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="33"/>
+    </row>
+    <row r="37" customHeight="1" spans="1:3">
+      <c r="A37" s="34">
+        <v>0</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C37" s="33"/>
+    </row>
+    <row r="38" customHeight="1" spans="1:3">
+      <c r="A38" s="34">
+        <v>0</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="33"/>
+    </row>
+    <row r="39" customHeight="1" spans="1:3">
+      <c r="A39" s="34">
+        <v>0</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="33"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:3">
+      <c r="A40" s="1">
+        <v>0</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="36"/>
+    </row>
+    <row r="41" customHeight="1" spans="2:3">
+      <c r="B41" s="35"/>
+      <c r="C41" s="37"/>
+    </row>
+    <row r="42" customHeight="1" spans="2:3">
+      <c r="B42" s="35"/>
+      <c r="C42" s="37"/>
+    </row>
+    <row r="43" customHeight="1" spans="1:3">
+      <c r="A43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:3">
+      <c r="A44" s="1">
+        <v>4333</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:3">
+      <c r="A45" s="1">
+        <v>8500</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:3">
+      <c r="A46" s="1">
+        <v>2500</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="33" t="s">
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店流水表.xlsx
+++ b/财务与流水/馋唻买-听涛路店流水表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15220" tabRatio="723" firstSheet="2" activeTab="10"/>
+    <workbookView windowHeight="15220" tabRatio="723" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="开店成本清单" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1080" uniqueCount="224">
   <si>
     <t>总预算(元)</t>
   </si>
@@ -1937,8 +1937,8 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="支出明细26049_1119141618" displayName="支出明细26049_1119141618" ref="A43:C52">
-  <autoFilter ref="A43:C52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="支出明细26049_1119141618" displayName="支出明细26049_1119141618" ref="A43:C53">
+  <autoFilter ref="A43:C53"/>
   <tableColumns count="3">
     <tableColumn id="1" name="支出明细"/>
     <tableColumn id="2" name="分类"/>
@@ -2856,7 +2856,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultColWidth="30.625" defaultRowHeight="25.15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="30.625" style="1" customWidth="1"/>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B4" s="11">
         <f>SUM(支出明细26049_1119141618[支出明细])</f>
-        <v>23049.5</v>
+        <v>24595.5</v>
       </c>
       <c r="C4" s="12" t="s">
         <v>49</v>
@@ -2912,7 +2912,7 @@
       </c>
       <c r="B5" s="14">
         <f>$B$3-SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
-        <v>-7716.5</v>
+        <v>-9262.5</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>49</v>
@@ -2924,7 +2924,7 @@
       </c>
       <c r="B6" s="14">
         <f>$B$3-$B$4</f>
-        <v>-23049.5</v>
+        <v>-24595.5</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>49</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="B24" s="14">
         <f>SUMIF(支出明细26049_1119141618[分类],"食材",支出明细26049_1119141618[支出明细])</f>
-        <v>7716.5</v>
+        <v>9262.5</v>
       </c>
       <c r="C24" s="16">
         <f>$B$24/$B$4</f>
-        <v>0.334779496301438</v>
+        <v>0.376593279258401</v>
       </c>
     </row>
     <row r="25" customHeight="1" spans="1:3">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="C25" s="16">
         <f>$B$25/$B$4</f>
-        <v>0.368771556866743</v>
+        <v>0.345591673273566</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:3">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="C26" s="16">
         <f>$B$26/$B$4</f>
-        <v>0.187986724223953</v>
+        <v>0.17617043768169</v>
       </c>
     </row>
     <row r="27" customHeight="1" spans="1:3">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C28" s="16">
         <f>$B$28/$B$4</f>
-        <v>0.108462222607866</v>
+        <v>0.101644609786343</v>
       </c>
     </row>
     <row r="29" customHeight="1" spans="1:3">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B30" s="30">
         <f>SUM(B24:B29)</f>
-        <v>23049.5</v>
+        <v>24595.5</v>
       </c>
       <c r="C30" s="31">
         <f>SUM($C$24:$C$29)</f>
@@ -3365,6 +3365,28 @@
       </c>
       <c r="C51" s="2" t="s">
         <v>223</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="1:3">
+      <c r="A52" s="1">
+        <v>1000</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:3">
+      <c r="A53" s="1">
+        <v>546</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3375,7 +3397,7 @@
     <mergeCell ref="A23:C23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B2:B7 B44:B46">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B47 B48 B49 B50 B51 B52 B53 B2:B7 B44:B46">
       <formula1>"房租,其他,食材,推广,水电,工资"</formula1>
     </dataValidation>
   </dataValidations>
